--- a/results/06-2026/beta/contributions-comparison-06-2026.xlsx
+++ b/results/06-2026/beta/contributions-comparison-06-2026.xlsx
@@ -2675,10 +2675,10 @@
         <v>0.000551965031565569</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.993610612244152</v>
+        <v>-0.563901926533413</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.400332757045023</v>
+        <v>-0.0293759286657161</v>
       </c>
       <c r="AA22" t="n">
         <v>-0.0973949910447126</v>
@@ -2773,10 +2773,10 @@
         <v>-0.0299392802978311</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.937821968966787</v>
+        <v>-0.941736425915037</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.531980090246069</v>
+        <v>0.535894547194319</v>
       </c>
       <c r="AA23" t="n">
         <v>-0.274529505412121</v>
@@ -2871,10 +2871,10 @@
         <v>0.0465164147221872</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.273885378533513</v>
+        <v>-1.02320131401768</v>
       </c>
       <c r="Z24" t="n">
-        <v>-0.275751448037125</v>
+        <v>1.02133524451407</v>
       </c>
       <c r="AA24" t="n">
         <v>-0.139229581720164</v>
@@ -2969,10 +2969,10 @@
         <v>0.0427711776553399</v>
       </c>
       <c r="Y25" t="n">
-        <v>-1.57957660760554</v>
+        <v>-1.56878037182218</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.261833944831957</v>
+        <v>0.251037709048592</v>
       </c>
       <c r="AA25" t="n">
         <v>-0.236364588453239</v>
@@ -3067,10 +3067,10 @@
         <v>0.0279219275040355</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.25947181449783</v>
+        <v>0.45679544563831</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.632213338315575</v>
+        <v>-0.0840539218205656</v>
       </c>
       <c r="AA26" t="n">
         <v>0.518830766937432</v>
@@ -3165,10 +3165,10 @@
         <v>0.0298460339594499</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.5671038059027</v>
+        <v>-0.310038277709138</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.144000003691044</v>
+        <v>-0.113065524502518</v>
       </c>
       <c r="AA27" t="n">
         <v>0.495558685442469</v>
@@ -3263,10 +3263,10 @@
         <v>-0.0327728224575521</v>
       </c>
       <c r="Y28" t="n">
-        <v>-0.320220152545529</v>
+        <v>-0.321933384762828</v>
       </c>
       <c r="Z28" t="n">
-        <v>-0.161629668840258</v>
+        <v>-0.159916436622958</v>
       </c>
       <c r="AA28" t="n">
         <v>0.259332692885168</v>
@@ -3361,10 +3361,10 @@
         <v>-0.0188333683503671</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.144054229428114</v>
+        <v>-0.145712300878208</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.161885268446017</v>
+        <v>-0.160227196995923</v>
       </c>
       <c r="AA29" t="n">
         <v>-0.0497318544737479</v>
@@ -3459,10 +3459,10 @@
         <v>-0.0237955709487201</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.138489424399087</v>
+        <v>-0.140129793493637</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.160775647597551</v>
+        <v>-0.159135278503001</v>
       </c>
       <c r="AA30" t="n">
         <v>-0.52205252025133</v>
@@ -3557,10 +3557,10 @@
         <v>-0.0120783940754789</v>
       </c>
       <c r="Y31" t="n">
-        <v>-0.121008626134354</v>
+        <v>-0.122605259151308</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.156456728074844</v>
+        <v>-0.15486009505789</v>
       </c>
       <c r="AA31" t="n">
         <v>-0.472376041617324</v>
@@ -3655,10 +3655,10 @@
         <v>-0.0227902971602149</v>
       </c>
       <c r="Y32" t="n">
-        <v>-0.126451889857658</v>
+        <v>-0.128004915214177</v>
       </c>
       <c r="Z32" t="n">
-        <v>-0.164869728202617</v>
+        <v>-0.163316702846099</v>
       </c>
       <c r="AA32" t="n">
         <v>-0.249918399898359</v>
@@ -3753,10 +3753,10 @@
         <v>-0.0119661510489623</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.192860170360113</v>
+        <v>-0.194375766997843</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.162294420893371</v>
+        <v>-0.160778824255641</v>
       </c>
       <c r="AA33" t="n">
         <v>-0.252151394022548</v>
@@ -3851,10 +3851,10 @@
         <v>0.00577189183083751</v>
       </c>
       <c r="Y34" t="n">
-        <v>-0.225108545398582</v>
+        <v>-0.226594695231705</v>
       </c>
       <c r="Z34" t="n">
-        <v>-0.16203894718382</v>
+        <v>-0.160552797350697</v>
       </c>
       <c r="AA34" t="n">
         <v>-0.606161522208577</v>
@@ -9319,10 +9319,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.429708685710739</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.429708685710739</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -9415,10 +9415,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.00391445694824999</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>-0.00391445694824999</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -9511,10 +9511,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.29708669255119</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>-1.2970866925512</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -9607,10 +9607,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>-0.01079623578336</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.010796235783365</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -9703,10 +9703,10 @@
         <v>0.0338923160191173</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.71568639405069</v>
+        <v>0.000580866085449994</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.728135681058546</v>
+        <v>0.0118684209224049</v>
       </c>
       <c r="AA26" t="n">
         <v>0.00549144546717806</v>
@@ -9799,10 +9799,10 @@
         <v>0.0099990815300495</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.256568209599349</v>
+        <v>0.000497318594212981</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.25721298533254</v>
+        <v>0.000147457138977999</v>
       </c>
       <c r="AA27" t="n">
         <v>-0.007042156411665</v>
@@ -9895,10 +9895,10 @@
         <v>0.0124959516601742</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.00218811228745702</v>
+        <v>0.000474880070158001</v>
       </c>
       <c r="Z28" t="n">
-        <v>-0.00149714494727701</v>
+        <v>0.00021608727002298</v>
       </c>
       <c r="AA28" t="n">
         <v>-0.00629759849644895</v>
@@ -9991,10 +9991,10 @@
         <v>0.0140688776876498</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.001872041234041</v>
+        <v>0.000213969783946999</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.001446796287222</v>
+        <v>0.000211275162872004</v>
       </c>
       <c r="AA29" t="n">
         <v>-0.0028542304012554</v>
@@ -10087,10 +10087,10 @@
         <v>-0.0166192823218324</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.001847316670853</v>
+        <v>0.000206947576303018</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.00142829251524001</v>
+        <v>0.000212076579309994</v>
       </c>
       <c r="AA30" t="n">
         <v>-0.00221055143435001</v>
@@ -10183,10 +10183,10 @@
         <v>0.0034334380471242</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.00177652931819601</v>
+        <v>0.000179896301242002</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.00139066797457801</v>
+        <v>0.000205965042375994</v>
       </c>
       <c r="AA31" t="n">
         <v>-0.00223870182369201</v>
@@ -10279,10 +10279,10 @@
         <v>0.0015777212411767</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.00174260411343499</v>
+        <v>0.000189578756915998</v>
       </c>
       <c r="Z32" t="n">
-        <v>-0.00133690445454801</v>
+        <v>0.000216120901969985</v>
       </c>
       <c r="AA32" t="n">
         <v>-0.00249221987190701</v>
@@ -10375,10 +10375,10 @@
         <v>-0.000705350952906901</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.001812428907423</v>
+        <v>0.000296832269692987</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.00130324474031501</v>
+        <v>0.000212351897415003</v>
       </c>
       <c r="AA33" t="n">
         <v>-0.00245562415331899</v>
@@ -10471,10 +10471,10 @@
         <v>-0.00367911380843939</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.001835199745399</v>
+        <v>0.000349049912275995</v>
       </c>
       <c r="Z34" t="n">
-        <v>-0.00127442698237401</v>
+        <v>0.000211722850748997</v>
       </c>
       <c r="AA34" t="n">
         <v>-0.00165978768152097</v>

--- a/results/06-2026/beta/contributions-comparison-06-2026.xlsx
+++ b/results/06-2026/beta/contributions-comparison-06-2026.xlsx
@@ -3108,7 +3108,7 @@
         <v>-0.177275710542129</v>
       </c>
       <c r="F27" t="n">
-        <v>0.121528970243519</v>
+        <v>0.0934153245580765</v>
       </c>
       <c r="G27" t="n">
         <v>-0.0296502192522053</v>
@@ -3171,22 +3171,22 @@
         <v>-0.113065524502518</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.495558685442469</v>
+        <v>0.467555812719875</v>
       </c>
       <c r="AB27" t="n">
         <v>-0.210068495709401</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.346584853288415</v>
+        <v>0.318520072724498</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.244089996852817</v>
+        <v>0.216087124130223</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.0765189489232416</v>
+        <v>-0.104583729487159</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.0395258909192063</v>
+        <v>-0.0465420860601855</v>
       </c>
     </row>
     <row r="28">
@@ -3206,7 +3206,7 @@
         <v>-0.176127949318067</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0550873494343489</v>
+        <v>0.0276004019594846</v>
       </c>
       <c r="G28" t="n">
         <v>-0.0281345637364049</v>
@@ -3269,22 +3269,22 @@
         <v>-0.159916436622958</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.259332692885168</v>
+        <v>0.23190505200772</v>
       </c>
       <c r="AB28" t="n">
         <v>-0.11344944776243</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.20619378956889</v>
+        <v>0.178733291340387</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.181425143618067</v>
+        <v>0.153997502740619</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.275656031816896</v>
+        <v>-0.3031165300454</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.173518630714225</v>
+        <v>-0.187399950412331</v>
       </c>
     </row>
     <row r="29">
@@ -3304,7 +3304,7 @@
         <v>-0.199823746473653</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.00019929095037767</v>
+        <v>-0.0134596169475721</v>
       </c>
       <c r="G29" t="n">
         <v>-0.0168163974913964</v>
@@ -3367,22 +3367,22 @@
         <v>-0.160227196995923</v>
       </c>
       <c r="AA29" t="n">
-        <v>-0.0497318544737479</v>
+        <v>-0.0629991340991395</v>
       </c>
       <c r="AB29" t="n">
         <v>-0.0816728725013126</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.0714477229295267</v>
+        <v>-0.0847264715812518</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.0025443668764997</v>
+        <v>-0.0107229127488918</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.377387220803658</v>
+        <v>-0.390665969455383</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.038194898251568</v>
+        <v>0.0209938913905315</v>
       </c>
     </row>
     <row r="30">
@@ -3402,7 +3402,7 @@
         <v>-0.18610015880645</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.268032786092446</v>
+        <v>-0.253688552873603</v>
       </c>
       <c r="G30" t="n">
         <v>-0.0163834111471112</v>
@@ -3465,22 +3465,22 @@
         <v>-0.159135278503001</v>
       </c>
       <c r="AA30" t="n">
-        <v>-0.52205252025133</v>
+        <v>-0.50766973421812</v>
       </c>
       <c r="AB30" t="n">
         <v>-0.00865652585666954</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.470757018499112</v>
+        <v>-0.456372911986712</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.255256447635832</v>
+        <v>-0.240873661602622</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.77002209049575</v>
+        <v>-0.75563798398335</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.374896073009886</v>
+        <v>-0.388501053242823</v>
       </c>
     </row>
     <row r="31">
@@ -3500,7 +3500,7 @@
         <v>-0.180630207192896</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.131970802297558</v>
+        <v>-0.1179177107918</v>
       </c>
       <c r="G31" t="n">
         <v>-0.0118967399948219</v>
@@ -3563,22 +3563,22 @@
         <v>-0.15486009505789</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.472376041617324</v>
+        <v>-0.458272130010322</v>
       </c>
       <c r="AB31" t="n">
         <v>0.0398427805528704</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.372332981737238</v>
+        <v>-0.358235045105774</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.108659366670345</v>
+        <v>-0.0945554550633428</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.649798335946436</v>
+        <v>-0.635700399314971</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.518215919765685</v>
+        <v>-0.521280220699776</v>
       </c>
     </row>
     <row r="32">
@@ -3598,7 +3598,7 @@
         <v>-0.187907680306217</v>
       </c>
       <c r="F32" t="n">
-        <v>0.113285402974249</v>
+        <v>0.113718617959926</v>
       </c>
       <c r="G32" t="n">
         <v>-0.00842644245736131</v>
@@ -3661,22 +3661,22 @@
         <v>-0.163316702846099</v>
       </c>
       <c r="AA32" t="n">
-        <v>-0.249918399898359</v>
+        <v>-0.249483509006717</v>
       </c>
       <c r="AB32" t="n">
         <v>-0.0388590418499953</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.288880728515349</v>
+        <v>-0.288445657970427</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.136398666383842</v>
+        <v>0.136833557275484</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.580202346575624</v>
+        <v>-0.579767276030702</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.594352498455367</v>
+        <v>-0.590442907196101</v>
       </c>
     </row>
     <row r="33">
@@ -3696,7 +3696,7 @@
         <v>-0.184381860922253</v>
       </c>
       <c r="F33" t="n">
-        <v>0.135482587160068</v>
+        <v>0.135905537440735</v>
       </c>
       <c r="G33" t="n">
         <v>0.00329475107119413</v>
@@ -3759,22 +3759,22 @@
         <v>-0.160778824255641</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.252151394022548</v>
+        <v>-0.251726694949662</v>
       </c>
       <c r="AB33" t="n">
         <v>0.0171152561285791</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.234990180772845</v>
+        <v>-0.234565559071119</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.176441298150528</v>
+        <v>0.176865997223414</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.590144772026329</v>
+        <v>-0.589720150324603</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.647541886261035</v>
+        <v>-0.640206452413406</v>
       </c>
     </row>
     <row r="34">
@@ -3794,7 +3794,7 @@
         <v>-0.183465051487523</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.0137078445556185</v>
+        <v>-0.013293126608685</v>
       </c>
       <c r="G34" t="n">
         <v>0.00134440690092982</v>
@@ -3857,22 +3857,22 @@
         <v>-0.160552797350697</v>
       </c>
       <c r="AA34" t="n">
-        <v>-0.606161522208577</v>
+        <v>-0.60574419090177</v>
       </c>
       <c r="AB34" t="n">
         <v>-0.0438103805367445</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.650254388885584</v>
+        <v>-0.64983686330003</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.0105372194990532</v>
+        <v>0.0109545508058604</v>
       </c>
       <c r="AE34" t="n">
-        <v>-1.03740188146799</v>
+        <v>-1.03698435588243</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.714386834004094</v>
+        <v>-0.710543045388177</v>
       </c>
     </row>
   </sheetData>
@@ -9742,7 +9742,7 @@
         <v>0.000226337409318988</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.00172875006373101</v>
+        <v>-0.0298423957491735</v>
       </c>
       <c r="G27" t="n">
         <v>-0.0050459851717871</v>
@@ -9805,22 +9805,22 @@
         <v>0.000147457138977999</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.007042156411665</v>
+        <v>-0.035045029134259</v>
       </c>
       <c r="AB27" t="n">
         <v>-0.015685499723991</v>
       </c>
       <c r="AC27" t="n">
-        <v>-0.022656837470853</v>
+        <v>-0.05072161803477</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.00667638097537301</v>
+        <v>-0.034679253697967</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.0220120617376634</v>
+        <v>-0.0500768423015808</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.0054842123923733</v>
+        <v>-0.0015319827486059</v>
       </c>
     </row>
     <row r="28">
@@ -9838,7 +9838,7 @@
         <v>0.000224872000993998</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.000828127551029401</v>
+        <v>-0.0283150750258937</v>
       </c>
       <c r="G28" t="n">
         <v>-0.0054304475706859</v>
@@ -9901,22 +9901,22 @@
         <v>0.00021608727002298</v>
       </c>
       <c r="AA28" t="n">
-        <v>-0.00629759849644895</v>
+        <v>-0.033725239373897</v>
       </c>
       <c r="AB28" t="n">
         <v>-0.01177131949577</v>
       </c>
       <c r="AC28" t="n">
-        <v>-0.018042488568454</v>
+        <v>-0.045502986796957</v>
       </c>
       <c r="AD28" t="n">
-        <v>-0.006184418072092</v>
+        <v>-0.03361205894954</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.017351521228273</v>
+        <v>-0.044812019456777</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.00114633208530501</v>
+        <v>-0.012734987612801</v>
       </c>
     </row>
     <row r="29">
@@ -9934,7 +9934,7 @@
         <v>0.000255125696345004</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.000735514058705315</v>
+        <v>-0.0139958400558997</v>
       </c>
       <c r="G29" t="n">
         <v>-0.0024413112695106</v>
@@ -9997,22 +9997,22 @@
         <v>0.000211275162872004</v>
       </c>
       <c r="AA29" t="n">
-        <v>-0.0028542304012554</v>
+        <v>-0.016121510026647</v>
       </c>
       <c r="AB29" t="n">
         <v>-0.0111735513042655</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.014035912772465</v>
+        <v>-0.0273146614241901</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.00293010373310856</v>
+        <v>-0.0161973833585001</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.013610667825647</v>
+        <v>-0.026889416477372</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.0022563348711065</v>
+        <v>-0.019457341732143</v>
       </c>
     </row>
     <row r="30">
@@ -10030,7 +10030,7 @@
         <v>0.000237604055790985</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.000403537677187038</v>
+        <v>0.013940695541656</v>
       </c>
       <c r="G30" t="n">
         <v>-0.0024050141913518</v>
@@ -10093,22 +10093,22 @@
         <v>0.000212076579309994</v>
       </c>
       <c r="AA30" t="n">
-        <v>-0.00221055143435001</v>
+        <v>0.01217223459886</v>
       </c>
       <c r="AB30" t="n">
         <v>-0.0444439644392843</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.046899315085362</v>
+        <v>-0.032515208572962</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.00259717675459498</v>
+        <v>0.011785609278615</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.046480290929749</v>
+        <v>-0.0320961844173491</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.024863635430333</v>
+        <v>-0.03846861566327</v>
       </c>
     </row>
     <row r="31">
@@ -10126,7 +10126,7 @@
         <v>0.000230620275140009</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000586554563765995</v>
+        <v>0.013466536941992</v>
       </c>
       <c r="G31" t="n">
         <v>-0.00237662803640054</v>
@@ -10189,22 +10189,22 @@
         <v>0.000205965042375994</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.00223870182369201</v>
+        <v>0.01186520978331</v>
       </c>
       <c r="AB31" t="n">
         <v>0.00435552390928039</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.00214016921744198</v>
+        <v>0.016238105848906</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.002765406750064</v>
+        <v>0.0113385048569382</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.00252603056105904</v>
+        <v>0.016623967192524</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.0187291123556521</v>
+        <v>-0.021793413289743</v>
       </c>
     </row>
     <row r="32">
@@ -10222,7 +10222,7 @@
         <v>0.000239911815452021</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.000897651663078008</v>
+        <v>-0.000464436677401009</v>
       </c>
       <c r="G32" t="n">
         <v>-0.00235833948275082</v>
@@ -10285,22 +10285,22 @@
         <v>0.000216120901969985</v>
       </c>
       <c r="AA32" t="n">
-        <v>-0.00249221987190701</v>
+        <v>-0.00205732898026501</v>
       </c>
       <c r="AB32" t="n">
         <v>0.0012796418273458</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.00121060165158204</v>
+        <v>-0.00077553110666001</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.00305156260844902</v>
+        <v>-0.00261667171680702</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.000804901992695006</v>
+        <v>-0.000369831447773028</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.014592457546758</v>
+        <v>-0.010682866287492</v>
       </c>
     </row>
     <row r="33">
@@ -10318,7 +10318,7 @@
         <v>0.000235410212706982</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.000919505605183002</v>
+        <v>-0.000496555324516007</v>
       </c>
       <c r="G33" t="n">
         <v>-0.00234838567978603</v>
@@ -10381,22 +10381,22 @@
         <v>0.000212351897415003</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.00245562415331899</v>
+        <v>-0.00203092508043298</v>
       </c>
       <c r="AB33" t="n">
         <v>-0.0021205105383126</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.00458115106831</v>
+        <v>-0.00415652936658401</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.00307598517610599</v>
+        <v>-0.00265128610321999</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.00407196690120193</v>
+        <v>-0.00364734519947596</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.012207782315647</v>
+        <v>-0.00487234846801798</v>
       </c>
     </row>
     <row r="34">
@@ -10414,7 +10414,7 @@
         <v>0.000234239672920994</v>
       </c>
       <c r="F34" t="n">
-        <v>0.00000544926548440121</v>
+        <v>0.0004201672124179</v>
       </c>
       <c r="G34" t="n">
         <v>-0.00275565181884243</v>
@@ -10477,22 +10477,22 @@
         <v>0.000211722850748997</v>
       </c>
       <c r="AA34" t="n">
-        <v>-0.00165978768152097</v>
+        <v>-0.00124245637471398</v>
       </c>
       <c r="AB34" t="n">
         <v>-0.0048293628526029</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.00652183189352096</v>
+        <v>-0.00610430630796699</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.0025512075778955</v>
+        <v>-0.0021338762710883</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.00596105913049993</v>
+        <v>-0.00554353354494008</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.00207797436583301</v>
+        <v>0.00176581425008393</v>
       </c>
     </row>
   </sheetData>
